--- a/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
@@ -710,15 +710,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45168.54423634843</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="2">
       <c r="E2" s="19" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -755,27 +752,6 @@
       </c>
       <c r="B10" s="6" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
@@ -878,7 +854,6 @@
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="18" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1" s="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
@@ -893,10 +868,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>

--- a/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
@@ -710,7 +710,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
@@ -710,7 +710,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
@@ -710,7 +710,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="2">

--- a/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLO ANTIGOTA DISMAY.xlsx
@@ -710,12 +710,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45266</v>
+        <v>45258.54558463585</v>
       </c>
     </row>
     <row r="2">
       <c r="E2" s="19" t="n"/>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -752,6 +755,27 @@
       </c>
       <c r="B10" s="6" t="n"/>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
@@ -787,7 +811,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>161.5</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="1">
@@ -807,7 +831,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>190.8</v>
+        <v>228.2</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="1">
@@ -827,7 +851,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>211</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="1">
@@ -854,6 +878,7 @@
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="18" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1" s="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
@@ -868,6 +893,10 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
